--- a/demo/demo-inventory.xlsx
+++ b/demo/demo-inventory.xlsx
@@ -563,7 +563,6 @@
           <t>Rack B-04</t>
         </is>
       </c>
-      <c r="L3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -613,7 +612,6 @@
           <t>Rack B-05</t>
         </is>
       </c>
-      <c r="L4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -663,7 +661,6 @@
           <t>Rack B-06</t>
         </is>
       </c>
-      <c r="L5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -771,7 +768,6 @@
           <t>Rack C-02</t>
         </is>
       </c>
-      <c r="L7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -821,7 +817,6 @@
           <t>Rack C-03</t>
         </is>
       </c>
-      <c r="L8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -925,7 +920,6 @@
           <t>Rack C-07</t>
         </is>
       </c>
-      <c r="L10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -979,7 +973,6 @@
           <t>Used U-12</t>
         </is>
       </c>
-      <c r="L11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1029,7 +1022,6 @@
           <t>Rack A-05</t>
         </is>
       </c>
-      <c r="L12" s="3" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -1195,7 +1187,6 @@
           <t>Rack A-09</t>
         </is>
       </c>
-      <c r="L15" s="3" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -1245,7 +1236,6 @@
           <t>Rack A-12</t>
         </is>
       </c>
-      <c r="L16" s="3" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -1295,7 +1285,6 @@
           <t>Rack A-02</t>
         </is>
       </c>
-      <c r="L17" s="3" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -1345,7 +1334,6 @@
           <t>Yard 1</t>
         </is>
       </c>
-      <c r="L18" s="3" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -1395,7 +1383,6 @@
           <t>Yard 1</t>
         </is>
       </c>
-      <c r="L19" s="3" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -1445,7 +1432,6 @@
           <t>Yard 2</t>
         </is>
       </c>
-      <c r="L20" s="3" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
@@ -1495,7 +1481,6 @@
           <t>Yard 3</t>
         </is>
       </c>
-      <c r="L21" s="3" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">

--- a/demo/demo-inventory.xlsx
+++ b/demo/demo-inventory.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L24"/>
+  <dimension ref="A1:L26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1645,6 +1645,114 @@
       <c r="L24" s="3" t="inlineStr">
         <is>
           <t>qty typed as a word: not synced</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>255/45R20</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Michelin</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Pilot Sport 4S</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Summer</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr"/>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>105Y</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>1525</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>2</v>
+      </c>
+      <c r="J25" t="n">
+        <v>389</v>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>Rack C-01</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>staggered front (X3 M)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>265/45R20</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Michelin</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Pilot Sport 4S</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Summer</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr"/>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>108Y</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>1525</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>2</v>
+      </c>
+      <c r="J26" t="n">
+        <v>409</v>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>Rack C-01</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>staggered rear (X3 M)</t>
         </is>
       </c>
     </row>
